--- a/master.xlsx
+++ b/master.xlsx
@@ -3728,7 +3728,7 @@
       </c>
       <c r="B9" s="79" t="inlineStr">
         <is>
-          <t>갱신/비갱신: ①갱신형명시→갱신 ②운전자→비갱신 ③9999→비갱신 ④총회차240초과→비갱신 ⑤납입년수≠보장년수→비갱신.</t>
+          <t>갱신/비갱신(제5조 정본 v498): ⓪실손=무조건 갱신 ①담보명·상품명 갱신형 명시→갱신 ②만기 9999(종신)→비갱신 ③납입기간=보장기간→갱신 / 다르면→비갱신(운전자도 동일·3열 KB·메리츠도 동일). ★폐기: 운전자→비갱신 · 총회차240초과→비갱신 · 삼성 예외.</t>
         </is>
       </c>
     </row>

--- a/master.xlsx
+++ b/master.xlsx
@@ -1566,7 +1566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J106"/>
+  <dimension ref="A1:J107"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col width="6.5" customWidth="1" style="77" min="1" max="1"/>
@@ -1953,7 +1953,7 @@
       <c r="A20" s="105" t="n"/>
       <c r="B20" s="40" t="inlineStr">
         <is>
-          <t>통합전이암</t>
+          <t>소액암</t>
         </is>
       </c>
       <c r="C20" s="142" t="n"/>
@@ -1963,21 +1963,24 @@
       <c r="G20" s="142" t="n"/>
       <c r="H20" s="142" t="n"/>
       <c r="I20" s="142" t="n"/>
-      <c r="J20" s="129" t="n"/>
+      <c r="J20" s="129">
+        <f>SUM(C20:I20)</f>
+        <v/>
+      </c>
     </row>
     <row r="21" ht="16.5" customHeight="1" s="77">
       <c r="A21" s="105" t="n"/>
-      <c r="B21" s="42" t="inlineStr">
-        <is>
-          <t>암주요치료비</t>
-        </is>
-      </c>
-      <c r="C21" s="143" t="n"/>
-      <c r="D21" s="143" t="n"/>
-      <c r="E21" s="143" t="n"/>
-      <c r="F21" s="143" t="n"/>
-      <c r="G21" s="143" t="n"/>
-      <c r="H21" s="143" t="n"/>
+      <c r="B21" s="40" t="inlineStr">
+        <is>
+          <t>통합전이암</t>
+        </is>
+      </c>
+      <c r="C21" s="142" t="n"/>
+      <c r="D21" s="142" t="n"/>
+      <c r="E21" s="142" t="n"/>
+      <c r="F21" s="142" t="n"/>
+      <c r="G21" s="142" t="n"/>
+      <c r="H21" s="142" t="n"/>
       <c r="I21" s="142" t="n"/>
       <c r="J21" s="129" t="n"/>
     </row>
@@ -1985,7 +1988,7 @@
       <c r="A22" s="105" t="n"/>
       <c r="B22" s="42" t="inlineStr">
         <is>
-          <t>10억 플랜</t>
+          <t>암주요치료비</t>
         </is>
       </c>
       <c r="C22" s="143" t="n"/>
@@ -2001,37 +2004,34 @@
       <c r="A23" s="105" t="n"/>
       <c r="B23" s="42" t="inlineStr">
         <is>
-          <t>하이클래스(암)</t>
-        </is>
-      </c>
-      <c r="C23" s="142" t="n"/>
-      <c r="D23" s="142" t="n"/>
-      <c r="E23" s="142" t="n"/>
-      <c r="F23" s="142" t="n"/>
-      <c r="G23" s="142" t="n"/>
-      <c r="H23" s="142" t="n"/>
+          <t>10억 플랜</t>
+        </is>
+      </c>
+      <c r="C23" s="143" t="n"/>
+      <c r="D23" s="143" t="n"/>
+      <c r="E23" s="143" t="n"/>
+      <c r="F23" s="143" t="n"/>
+      <c r="G23" s="143" t="n"/>
+      <c r="H23" s="143" t="n"/>
       <c r="I23" s="142" t="n"/>
-      <c r="J23" s="135">
-        <f>SUM(C21:I21)</f>
-        <v/>
-      </c>
+      <c r="J23" s="129" t="n"/>
     </row>
     <row r="24" ht="16.5" customHeight="1" s="77">
       <c r="A24" s="105" t="n"/>
       <c r="B24" s="42" t="inlineStr">
         <is>
-          <t>중입자치료비</t>
-        </is>
-      </c>
-      <c r="C24" s="143" t="n"/>
-      <c r="D24" s="143" t="n"/>
-      <c r="E24" s="143" t="n"/>
-      <c r="F24" s="143" t="n"/>
-      <c r="G24" s="143" t="n"/>
-      <c r="H24" s="143" t="n"/>
+          <t>하이클래스(암)</t>
+        </is>
+      </c>
+      <c r="C24" s="142" t="n"/>
+      <c r="D24" s="142" t="n"/>
+      <c r="E24" s="142" t="n"/>
+      <c r="F24" s="142" t="n"/>
+      <c r="G24" s="142" t="n"/>
+      <c r="H24" s="142" t="n"/>
       <c r="I24" s="142" t="n"/>
-      <c r="J24" s="129">
-        <f>SUM(C23:I23)</f>
+      <c r="J24" s="135">
+        <f>SUM(C22:I22)</f>
         <v/>
       </c>
     </row>
@@ -2039,7 +2039,7 @@
       <c r="A25" s="105" t="n"/>
       <c r="B25" s="42" t="inlineStr">
         <is>
-          <t>표적항암치료비</t>
+          <t>중입자치료비</t>
         </is>
       </c>
       <c r="C25" s="143" t="n"/>
@@ -2049,32 +2049,32 @@
       <c r="G25" s="143" t="n"/>
       <c r="H25" s="143" t="n"/>
       <c r="I25" s="142" t="n"/>
-      <c r="J25" s="129" t="n"/>
+      <c r="J25" s="129">
+        <f>SUM(C24:I24)</f>
+        <v/>
+      </c>
     </row>
     <row r="26" ht="16.5" customHeight="1" s="77">
       <c r="A26" s="105" t="n"/>
-      <c r="B26" s="44" t="inlineStr">
-        <is>
-          <t>양성자치료</t>
-        </is>
-      </c>
-      <c r="C26" s="144" t="n"/>
-      <c r="D26" s="144" t="n"/>
-      <c r="E26" s="144" t="n"/>
-      <c r="F26" s="144" t="n"/>
-      <c r="G26" s="144" t="n"/>
-      <c r="H26" s="144" t="n"/>
-      <c r="I26" s="145" t="n"/>
-      <c r="J26" s="135">
-        <f>SUM(C25:I25)</f>
-        <v/>
-      </c>
+      <c r="B26" s="42" t="inlineStr">
+        <is>
+          <t>표적항암치료비</t>
+        </is>
+      </c>
+      <c r="C26" s="143" t="n"/>
+      <c r="D26" s="143" t="n"/>
+      <c r="E26" s="143" t="n"/>
+      <c r="F26" s="143" t="n"/>
+      <c r="G26" s="143" t="n"/>
+      <c r="H26" s="143" t="n"/>
+      <c r="I26" s="142" t="n"/>
+      <c r="J26" s="129" t="n"/>
     </row>
     <row r="27" ht="16.5" customHeight="1" s="77">
       <c r="A27" s="105" t="n"/>
       <c r="B27" s="44" t="inlineStr">
         <is>
-          <t>세기조절치료</t>
+          <t>양성자치료</t>
         </is>
       </c>
       <c r="C27" s="144" t="n"/>
@@ -2093,7 +2093,7 @@
       <c r="A28" s="105" t="n"/>
       <c r="B28" s="44" t="inlineStr">
         <is>
-          <t>다빈치로봇수술비</t>
+          <t>세기조절치료</t>
         </is>
       </c>
       <c r="C28" s="144" t="n"/>
@@ -2112,192 +2112,192 @@
       <c r="A29" s="105" t="n"/>
       <c r="B29" s="44" t="inlineStr">
         <is>
-          <t>암수술</t>
-        </is>
-      </c>
-      <c r="C29" s="145" t="n"/>
-      <c r="D29" s="145" t="n"/>
-      <c r="E29" s="145" t="n"/>
-      <c r="F29" s="145" t="n"/>
-      <c r="G29" s="145" t="n"/>
-      <c r="H29" s="145" t="n"/>
+          <t>다빈치로봇수술비</t>
+        </is>
+      </c>
+      <c r="C29" s="144" t="n"/>
+      <c r="D29" s="144" t="n"/>
+      <c r="E29" s="144" t="n"/>
+      <c r="F29" s="144" t="n"/>
+      <c r="G29" s="144" t="n"/>
+      <c r="H29" s="144" t="n"/>
       <c r="I29" s="145" t="n"/>
       <c r="J29" s="135">
         <f>SUM(C28:I28)</f>
         <v/>
       </c>
     </row>
-    <row r="30" ht="17.25" customHeight="1" s="77">
+    <row r="30" ht="16.5" customHeight="1" s="77">
       <c r="A30" s="105" t="n"/>
-      <c r="B30" s="31" t="inlineStr">
-        <is>
-          <t>암일당</t>
-        </is>
-      </c>
-      <c r="C30" s="134" t="n"/>
-      <c r="D30" s="134" t="n"/>
-      <c r="E30" s="134" t="n"/>
-      <c r="F30" s="134" t="n"/>
-      <c r="G30" s="134" t="n"/>
-      <c r="H30" s="134" t="n"/>
-      <c r="I30" s="134" t="n"/>
+      <c r="B30" s="44" t="inlineStr">
+        <is>
+          <t>암수술</t>
+        </is>
+      </c>
+      <c r="C30" s="145" t="n"/>
+      <c r="D30" s="145" t="n"/>
+      <c r="E30" s="145" t="n"/>
+      <c r="F30" s="145" t="n"/>
+      <c r="G30" s="145" t="n"/>
+      <c r="H30" s="145" t="n"/>
+      <c r="I30" s="145" t="n"/>
       <c r="J30" s="135">
         <f>SUM(C29:I29)</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1" s="77">
-      <c r="A31" s="106" t="n"/>
-      <c r="B31" s="25" t="inlineStr">
+      <c r="A31" s="105" t="n"/>
+      <c r="B31" s="31" t="inlineStr">
+        <is>
+          <t>암일당</t>
+        </is>
+      </c>
+      <c r="C31" s="134" t="n"/>
+      <c r="D31" s="134" t="n"/>
+      <c r="E31" s="134" t="n"/>
+      <c r="F31" s="134" t="n"/>
+      <c r="G31" s="134" t="n"/>
+      <c r="H31" s="134" t="n"/>
+      <c r="I31" s="134" t="n"/>
+      <c r="J31" s="135">
+        <f>SUM(C30:I30)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" ht="17.25" customHeight="1" s="77">
+      <c r="A32" s="106" t="n"/>
+      <c r="B32" s="25" t="inlineStr">
         <is>
           <t>항암방사선약물</t>
         </is>
       </c>
-      <c r="C31" s="130" t="n"/>
-      <c r="D31" s="130" t="n"/>
-      <c r="E31" s="130" t="n"/>
-      <c r="F31" s="130" t="n"/>
-      <c r="G31" s="130" t="n"/>
-      <c r="H31" s="130" t="n"/>
-      <c r="I31" s="130" t="n"/>
-      <c r="J31" s="131">
-        <f>SUM(C30:I30)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32" ht="16.5" customHeight="1" s="77">
-      <c r="A32" s="104" t="inlineStr">
+      <c r="C32" s="130" t="n"/>
+      <c r="D32" s="130" t="n"/>
+      <c r="E32" s="130" t="n"/>
+      <c r="F32" s="130" t="n"/>
+      <c r="G32" s="130" t="n"/>
+      <c r="H32" s="130" t="n"/>
+      <c r="I32" s="130" t="n"/>
+      <c r="J32" s="131">
+        <f>SUM(C31:I31)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" ht="16.5" customHeight="1" s="77">
+      <c r="A33" s="104" t="inlineStr">
         <is>
           <t>뇌혈관</t>
         </is>
       </c>
-      <c r="B32" s="34" t="inlineStr">
+      <c r="B33" s="34" t="inlineStr">
         <is>
           <t>뇌혈관진단비</t>
         </is>
       </c>
-      <c r="C32" s="136" t="n"/>
-      <c r="D32" s="136" t="n"/>
-      <c r="E32" s="136" t="n"/>
-      <c r="F32" s="136" t="n"/>
-      <c r="G32" s="136" t="n"/>
-      <c r="H32" s="136" t="n"/>
-      <c r="I32" s="136" t="n"/>
-      <c r="J32" s="137">
-        <f>SUM(C31:I31)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33" ht="17.25" customHeight="1" s="77">
-      <c r="A33" s="105" t="n"/>
-      <c r="B33" s="47" t="inlineStr">
+      <c r="C33" s="136" t="n"/>
+      <c r="D33" s="136" t="n"/>
+      <c r="E33" s="136" t="n"/>
+      <c r="F33" s="136" t="n"/>
+      <c r="G33" s="136" t="n"/>
+      <c r="H33" s="136" t="n"/>
+      <c r="I33" s="136" t="n"/>
+      <c r="J33" s="137">
+        <f>SUM(C32:I32)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" ht="17.25" customHeight="1" s="77" thickBot="1">
+      <c r="A34" s="105" t="n"/>
+      <c r="B34" s="47" t="inlineStr">
         <is>
           <t>뇌졸증진단비</t>
         </is>
       </c>
-      <c r="C33" s="146" t="n"/>
-      <c r="D33" s="146" t="n"/>
-      <c r="E33" s="146" t="n"/>
-      <c r="F33" s="146" t="n"/>
-      <c r="G33" s="146" t="n"/>
-      <c r="H33" s="146" t="n"/>
-      <c r="I33" s="146" t="n"/>
-      <c r="J33" s="147">
-        <f>SUM(C32:I32)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34" ht="16.5" customHeight="1" s="77" thickBot="1">
-      <c r="A34" s="105" t="n"/>
-      <c r="B34" s="50" t="inlineStr">
-        <is>
-          <t>중대한 뇌졸증</t>
-        </is>
-      </c>
-      <c r="C34" s="141" t="n"/>
-      <c r="D34" s="141" t="n"/>
-      <c r="E34" s="141" t="n"/>
-      <c r="F34" s="141" t="n"/>
-      <c r="G34" s="141" t="n"/>
-      <c r="H34" s="141" t="n"/>
-      <c r="I34" s="141" t="n"/>
-      <c r="J34" s="148">
+      <c r="C34" s="146" t="n"/>
+      <c r="D34" s="146" t="n"/>
+      <c r="E34" s="146" t="n"/>
+      <c r="F34" s="146" t="n"/>
+      <c r="G34" s="146" t="n"/>
+      <c r="H34" s="146" t="n"/>
+      <c r="I34" s="146" t="n"/>
+      <c r="J34" s="147">
         <f>SUM(C33:I33)</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="16.5" customHeight="1" s="77">
       <c r="A35" s="105" t="n"/>
-      <c r="B35" s="95" t="inlineStr">
-        <is>
-          <t>뇌출혈진단비</t>
-        </is>
-      </c>
-      <c r="C35" s="149" t="n"/>
-      <c r="D35" s="149" t="n"/>
-      <c r="E35" s="149" t="n"/>
-      <c r="F35" s="149" t="n"/>
-      <c r="G35" s="149" t="n"/>
-      <c r="H35" s="149" t="n"/>
-      <c r="I35" s="149" t="n"/>
-      <c r="J35" s="150">
+      <c r="B35" s="50" t="inlineStr">
+        <is>
+          <t>중대한 뇌졸증</t>
+        </is>
+      </c>
+      <c r="C35" s="141" t="n"/>
+      <c r="D35" s="141" t="n"/>
+      <c r="E35" s="141" t="n"/>
+      <c r="F35" s="141" t="n"/>
+      <c r="G35" s="141" t="n"/>
+      <c r="H35" s="141" t="n"/>
+      <c r="I35" s="141" t="n"/>
+      <c r="J35" s="148">
         <f>SUM(C34:I34)</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="16.5" customHeight="1" s="77" thickBot="1">
       <c r="A36" s="105" t="n"/>
-      <c r="B36" s="98" t="inlineStr">
-        <is>
-          <t>중대한 뇌출혈</t>
-        </is>
-      </c>
-      <c r="C36" s="151" t="n"/>
-      <c r="D36" s="151" t="n"/>
-      <c r="E36" s="151" t="n"/>
-      <c r="F36" s="151" t="n"/>
-      <c r="G36" s="151" t="n"/>
-      <c r="H36" s="151" t="n"/>
-      <c r="I36" s="151" t="n"/>
-      <c r="J36" s="152">
+      <c r="B36" s="95" t="inlineStr">
+        <is>
+          <t>뇌출혈진단비</t>
+        </is>
+      </c>
+      <c r="C36" s="149" t="n"/>
+      <c r="D36" s="149" t="n"/>
+      <c r="E36" s="149" t="n"/>
+      <c r="F36" s="149" t="n"/>
+      <c r="G36" s="149" t="n"/>
+      <c r="H36" s="149" t="n"/>
+      <c r="I36" s="149" t="n"/>
+      <c r="J36" s="150">
         <f>SUM(C35:I35)</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="16.5" customHeight="1" s="77">
       <c r="A37" s="105" t="n"/>
-      <c r="B37" s="52" t="inlineStr">
-        <is>
-          <t>외상성뇌출혈</t>
-        </is>
-      </c>
-      <c r="C37" s="153" t="n"/>
-      <c r="D37" s="153" t="n"/>
-      <c r="E37" s="153" t="n"/>
-      <c r="F37" s="153" t="n"/>
-      <c r="G37" s="153" t="n"/>
-      <c r="H37" s="153" t="n"/>
-      <c r="I37" s="153" t="n"/>
-      <c r="J37" s="129">
-        <f>SUM(C35:I35)</f>
+      <c r="B37" s="98" t="inlineStr">
+        <is>
+          <t>중대한 뇌출혈</t>
+        </is>
+      </c>
+      <c r="C37" s="151" t="n"/>
+      <c r="D37" s="151" t="n"/>
+      <c r="E37" s="151" t="n"/>
+      <c r="F37" s="151" t="n"/>
+      <c r="G37" s="151" t="n"/>
+      <c r="H37" s="151" t="n"/>
+      <c r="I37" s="151" t="n"/>
+      <c r="J37" s="152">
+        <f>SUM(C36:I36)</f>
         <v/>
       </c>
     </row>
     <row r="38" ht="16.5" customHeight="1" s="77">
       <c r="A38" s="105" t="n"/>
-      <c r="B38" s="54" t="inlineStr">
-        <is>
-          <t>산정특례뇌혈관</t>
-        </is>
-      </c>
-      <c r="C38" s="154" t="n"/>
-      <c r="D38" s="154" t="n"/>
-      <c r="E38" s="154" t="n"/>
-      <c r="F38" s="154" t="n"/>
-      <c r="G38" s="154" t="n"/>
-      <c r="H38" s="154" t="n"/>
-      <c r="I38" s="154" t="n"/>
-      <c r="J38" s="135">
+      <c r="B38" s="52" t="inlineStr">
+        <is>
+          <t>외상성뇌출혈</t>
+        </is>
+      </c>
+      <c r="C38" s="153" t="n"/>
+      <c r="D38" s="153" t="n"/>
+      <c r="E38" s="153" t="n"/>
+      <c r="F38" s="153" t="n"/>
+      <c r="G38" s="153" t="n"/>
+      <c r="H38" s="153" t="n"/>
+      <c r="I38" s="153" t="n"/>
+      <c r="J38" s="129">
         <f>SUM(C36:I36)</f>
         <v/>
       </c>
@@ -2306,7 +2306,7 @@
       <c r="A39" s="105" t="n"/>
       <c r="B39" s="54" t="inlineStr">
         <is>
-          <t>2대 주요치료비</t>
+          <t>산정특례뇌혈관</t>
         </is>
       </c>
       <c r="C39" s="154" t="n"/>
@@ -2322,71 +2322,71 @@
       </c>
     </row>
     <row r="40" ht="16.5" customHeight="1" s="77" thickBot="1">
-      <c r="A40" s="106" t="n"/>
-      <c r="B40" s="56" t="inlineStr">
+      <c r="A40" s="105" t="n"/>
+      <c r="B40" s="54" t="inlineStr">
+        <is>
+          <t>2대 주요치료비</t>
+        </is>
+      </c>
+      <c r="C40" s="154" t="n"/>
+      <c r="D40" s="154" t="n"/>
+      <c r="E40" s="154" t="n"/>
+      <c r="F40" s="154" t="n"/>
+      <c r="G40" s="154" t="n"/>
+      <c r="H40" s="154" t="n"/>
+      <c r="I40" s="154" t="n"/>
+      <c r="J40" s="135">
+        <f>SUM(C38:I38)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41" ht="16.5" customHeight="1" s="77" thickBot="1">
+      <c r="A41" s="106" t="n"/>
+      <c r="B41" s="56" t="inlineStr">
         <is>
           <t>혈전용해치료비</t>
         </is>
       </c>
-      <c r="C40" s="130" t="n"/>
-      <c r="D40" s="130" t="n"/>
-      <c r="E40" s="130" t="n"/>
-      <c r="F40" s="130" t="n"/>
-      <c r="G40" s="130" t="n"/>
-      <c r="H40" s="130" t="n"/>
-      <c r="I40" s="130" t="n"/>
-      <c r="J40" s="131">
-        <f>SUM(C37:I37)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41" ht="16.5" customHeight="1" s="77" thickBot="1">
-      <c r="A41" s="104" t="inlineStr">
+      <c r="C41" s="130" t="n"/>
+      <c r="D41" s="130" t="n"/>
+      <c r="E41" s="130" t="n"/>
+      <c r="F41" s="130" t="n"/>
+      <c r="G41" s="130" t="n"/>
+      <c r="H41" s="130" t="n"/>
+      <c r="I41" s="130" t="n"/>
+      <c r="J41" s="131">
+        <f>SUM(C38:I38)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42" ht="16.5" customHeight="1" s="77">
+      <c r="A42" s="104" t="inlineStr">
         <is>
           <t>심장</t>
         </is>
       </c>
-      <c r="B41" s="28" t="inlineStr">
+      <c r="B42" s="28" t="inlineStr">
         <is>
           <t>협심증</t>
         </is>
       </c>
-      <c r="C41" s="115" t="n"/>
-      <c r="D41" s="115" t="n"/>
-      <c r="E41" s="115" t="n"/>
-      <c r="F41" s="115" t="n"/>
-      <c r="G41" s="115" t="n"/>
-      <c r="H41" s="115" t="n"/>
-      <c r="I41" s="115" t="n"/>
-      <c r="J41" s="133">
-        <f>SUM(C38:I38)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42" ht="16.5" customHeight="1" s="77">
-      <c r="A42" s="105" t="n"/>
-      <c r="B42" s="31" t="inlineStr">
-        <is>
-          <t>심부전</t>
-        </is>
-      </c>
-      <c r="C42" s="145" t="n"/>
-      <c r="D42" s="145" t="n"/>
-      <c r="E42" s="145" t="n"/>
-      <c r="F42" s="145" t="n"/>
-      <c r="G42" s="145" t="n"/>
-      <c r="H42" s="145" t="n"/>
-      <c r="I42" s="145" t="n"/>
-      <c r="J42" s="135">
+      <c r="C42" s="115" t="n"/>
+      <c r="D42" s="115" t="n"/>
+      <c r="E42" s="115" t="n"/>
+      <c r="F42" s="115" t="n"/>
+      <c r="G42" s="115" t="n"/>
+      <c r="H42" s="115" t="n"/>
+      <c r="I42" s="115" t="n"/>
+      <c r="J42" s="133">
         <f>SUM(C39:I39)</f>
         <v/>
       </c>
     </row>
-    <row r="43" ht="17.25" customHeight="1" s="77">
+    <row r="43" ht="16.5" customHeight="1" s="77">
       <c r="A43" s="105" t="n"/>
       <c r="B43" s="31" t="inlineStr">
         <is>
-          <t>빈맥</t>
+          <t>심부전</t>
         </is>
       </c>
       <c r="C43" s="145" t="n"/>
@@ -2396,13 +2396,16 @@
       <c r="G43" s="145" t="n"/>
       <c r="H43" s="145" t="n"/>
       <c r="I43" s="145" t="n"/>
-      <c r="J43" s="135" t="n"/>
-    </row>
-    <row r="44" ht="16.5" customHeight="1" s="77">
+      <c r="J43" s="135">
+        <f>SUM(C40:I40)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44" ht="17.25" customHeight="1" s="77">
       <c r="A44" s="105" t="n"/>
       <c r="B44" s="31" t="inlineStr">
         <is>
-          <t>염증</t>
+          <t>빈맥</t>
         </is>
       </c>
       <c r="C44" s="145" t="n"/>
@@ -2412,54 +2415,54 @@
       <c r="G44" s="145" t="n"/>
       <c r="H44" s="145" t="n"/>
       <c r="I44" s="145" t="n"/>
-      <c r="J44" s="135">
-        <f>SUM(C40:I40)</f>
-        <v/>
-      </c>
+      <c r="J44" s="135" t="n"/>
     </row>
     <row r="45" ht="16.5" customHeight="1" s="77">
       <c r="A45" s="105" t="n"/>
-      <c r="B45" s="40" t="inlineStr">
-        <is>
-          <t>부정맥</t>
-        </is>
-      </c>
-      <c r="C45" s="155" t="n"/>
-      <c r="D45" s="155" t="n"/>
-      <c r="E45" s="155" t="n"/>
-      <c r="F45" s="155" t="n"/>
-      <c r="G45" s="155" t="n"/>
-      <c r="H45" s="155" t="n"/>
-      <c r="I45" s="155" t="n"/>
+      <c r="B45" s="31" t="inlineStr">
+        <is>
+          <t>염증</t>
+        </is>
+      </c>
+      <c r="C45" s="145" t="n"/>
+      <c r="D45" s="145" t="n"/>
+      <c r="E45" s="145" t="n"/>
+      <c r="F45" s="145" t="n"/>
+      <c r="G45" s="145" t="n"/>
+      <c r="H45" s="145" t="n"/>
+      <c r="I45" s="145" t="n"/>
       <c r="J45" s="135">
         <f>SUM(C41:I41)</f>
         <v/>
       </c>
     </row>
-    <row r="46" ht="17.25" customHeight="1" s="77">
+    <row r="46" ht="16.5" customHeight="1" s="77">
       <c r="A46" s="105" t="n"/>
-      <c r="B46" s="58" t="inlineStr">
-        <is>
-          <t>심근병증</t>
-        </is>
-      </c>
-      <c r="C46" s="89" t="n"/>
-      <c r="D46" s="89" t="n"/>
-      <c r="E46" s="89" t="n"/>
-      <c r="F46" s="89" t="n"/>
-      <c r="G46" s="89" t="n"/>
-      <c r="H46" s="89" t="n"/>
-      <c r="I46" s="89" t="n"/>
-      <c r="J46" s="91" t="n"/>
+      <c r="B46" s="40" t="inlineStr">
+        <is>
+          <t>부정맥</t>
+        </is>
+      </c>
+      <c r="C46" s="155" t="n"/>
+      <c r="D46" s="155" t="n"/>
+      <c r="E46" s="155" t="n"/>
+      <c r="F46" s="155" t="n"/>
+      <c r="G46" s="155" t="n"/>
+      <c r="H46" s="155" t="n"/>
+      <c r="I46" s="155" t="n"/>
+      <c r="J46" s="135">
+        <f>SUM(C42:I42)</f>
+        <v/>
+      </c>
     </row>
     <row r="47" ht="17.25" customHeight="1" s="77">
       <c r="A47" s="105" t="n"/>
-      <c r="B47" s="40" t="inlineStr">
-        <is>
-          <t>심장판막</t>
-        </is>
-      </c>
-      <c r="C47" s="90" t="n"/>
+      <c r="B47" s="58" t="inlineStr">
+        <is>
+          <t>심근병증</t>
+        </is>
+      </c>
+      <c r="C47" s="89" t="n"/>
       <c r="D47" s="89" t="n"/>
       <c r="E47" s="89" t="n"/>
       <c r="F47" s="89" t="n"/>
@@ -2468,158 +2471,155 @@
       <c r="I47" s="89" t="n"/>
       <c r="J47" s="91" t="n"/>
     </row>
-    <row r="48" ht="16.5" customHeight="1" s="77" thickBot="1">
+    <row r="48" ht="17.25" customHeight="1" s="77" thickBot="1">
       <c r="A48" s="105" t="n"/>
-      <c r="B48" s="81" t="inlineStr">
-        <is>
-          <t>허혈성 진단비</t>
-        </is>
-      </c>
-      <c r="C48" s="128" t="n"/>
-      <c r="D48" s="128" t="n"/>
-      <c r="E48" s="128" t="n"/>
-      <c r="F48" s="128" t="n"/>
-      <c r="G48" s="128" t="n"/>
-      <c r="H48" s="128" t="n"/>
-      <c r="I48" s="128" t="n"/>
-      <c r="J48" s="135">
-        <f>SUM(C44:I44)</f>
-        <v/>
-      </c>
+      <c r="B48" s="40" t="inlineStr">
+        <is>
+          <t>심장판막</t>
+        </is>
+      </c>
+      <c r="C48" s="90" t="n"/>
+      <c r="D48" s="89" t="n"/>
+      <c r="E48" s="89" t="n"/>
+      <c r="F48" s="89" t="n"/>
+      <c r="G48" s="89" t="n"/>
+      <c r="H48" s="89" t="n"/>
+      <c r="I48" s="89" t="n"/>
+      <c r="J48" s="91" t="n"/>
     </row>
     <row r="49" ht="16.5" customHeight="1" s="77">
       <c r="A49" s="105" t="n"/>
-      <c r="B49" s="13" t="inlineStr">
-        <is>
-          <t>급성심근경색</t>
-        </is>
-      </c>
-      <c r="C49" s="138" t="n"/>
-      <c r="D49" s="138" t="n"/>
-      <c r="E49" s="138" t="n"/>
-      <c r="F49" s="138" t="n"/>
-      <c r="G49" s="138" t="n"/>
-      <c r="H49" s="138" t="n"/>
-      <c r="I49" s="138" t="n"/>
-      <c r="J49" s="123">
-        <f>SUM(C44:I44)</f>
+      <c r="B49" s="81" t="inlineStr">
+        <is>
+          <t>허혈성 진단비</t>
+        </is>
+      </c>
+      <c r="C49" s="128" t="n"/>
+      <c r="D49" s="128" t="n"/>
+      <c r="E49" s="128" t="n"/>
+      <c r="F49" s="128" t="n"/>
+      <c r="G49" s="128" t="n"/>
+      <c r="H49" s="128" t="n"/>
+      <c r="I49" s="128" t="n"/>
+      <c r="J49" s="135">
+        <f>SUM(C45:I45)</f>
         <v/>
       </c>
     </row>
     <row r="50" ht="16.5" customHeight="1" s="77" thickBot="1">
       <c r="A50" s="105" t="n"/>
-      <c r="B50" s="16" t="inlineStr">
-        <is>
-          <t>중대한 급성심근</t>
-        </is>
-      </c>
-      <c r="C50" s="124" t="n"/>
-      <c r="D50" s="124" t="n"/>
-      <c r="E50" s="124" t="n"/>
-      <c r="F50" s="124" t="n"/>
-      <c r="G50" s="124" t="n"/>
-      <c r="H50" s="124" t="n"/>
-      <c r="I50" s="124" t="n"/>
-      <c r="J50" s="148">
-        <f>SUM(C46:I46)</f>
+      <c r="B50" s="13" t="inlineStr">
+        <is>
+          <t>급성심근경색</t>
+        </is>
+      </c>
+      <c r="C50" s="138" t="n"/>
+      <c r="D50" s="138" t="n"/>
+      <c r="E50" s="138" t="n"/>
+      <c r="F50" s="138" t="n"/>
+      <c r="G50" s="138" t="n"/>
+      <c r="H50" s="138" t="n"/>
+      <c r="I50" s="138" t="n"/>
+      <c r="J50" s="123">
+        <f>SUM(C45:I45)</f>
         <v/>
       </c>
     </row>
     <row r="51" ht="16.5" customHeight="1" s="77">
       <c r="A51" s="105" t="n"/>
-      <c r="B51" s="54" t="inlineStr">
-        <is>
-          <t>2대 주요치료비</t>
-        </is>
-      </c>
-      <c r="C51" s="154" t="n"/>
-      <c r="D51" s="154" t="n"/>
-      <c r="E51" s="154" t="n"/>
-      <c r="F51" s="154" t="n"/>
-      <c r="G51" s="154" t="n"/>
-      <c r="H51" s="154" t="n"/>
-      <c r="I51" s="154" t="n"/>
-      <c r="J51" s="135">
-        <f>SUM(C49:I49)</f>
+      <c r="B51" s="16" t="inlineStr">
+        <is>
+          <t>중대한 급성심근</t>
+        </is>
+      </c>
+      <c r="C51" s="124" t="n"/>
+      <c r="D51" s="124" t="n"/>
+      <c r="E51" s="124" t="n"/>
+      <c r="F51" s="124" t="n"/>
+      <c r="G51" s="124" t="n"/>
+      <c r="H51" s="124" t="n"/>
+      <c r="I51" s="124" t="n"/>
+      <c r="J51" s="148">
+        <f>SUM(C47:I47)</f>
         <v/>
       </c>
     </row>
     <row r="52" ht="16.5" customHeight="1" s="77">
       <c r="A52" s="105" t="n"/>
-      <c r="B52" s="101" t="inlineStr">
-        <is>
-          <t>산정특례심장</t>
-        </is>
-      </c>
-      <c r="C52" s="145" t="n"/>
-      <c r="D52" s="145" t="n"/>
-      <c r="E52" s="145" t="n"/>
-      <c r="F52" s="145" t="n"/>
-      <c r="G52" s="145" t="n"/>
-      <c r="H52" s="145" t="n"/>
-      <c r="I52" s="145" t="n"/>
+      <c r="B52" s="54" t="inlineStr">
+        <is>
+          <t>2대 주요치료비</t>
+        </is>
+      </c>
+      <c r="C52" s="154" t="n"/>
+      <c r="D52" s="154" t="n"/>
+      <c r="E52" s="154" t="n"/>
+      <c r="F52" s="154" t="n"/>
+      <c r="G52" s="154" t="n"/>
+      <c r="H52" s="154" t="n"/>
+      <c r="I52" s="154" t="n"/>
       <c r="J52" s="135">
         <f>SUM(C50:I50)</f>
         <v/>
       </c>
     </row>
     <row r="53" ht="16.5" customHeight="1" s="77" thickBot="1">
-      <c r="A53" s="106" t="n"/>
-      <c r="B53" s="62" t="inlineStr">
+      <c r="A53" s="105" t="n"/>
+      <c r="B53" s="101" t="inlineStr">
+        <is>
+          <t>산정특례심장</t>
+        </is>
+      </c>
+      <c r="C53" s="145" t="n"/>
+      <c r="D53" s="145" t="n"/>
+      <c r="E53" s="145" t="n"/>
+      <c r="F53" s="145" t="n"/>
+      <c r="G53" s="145" t="n"/>
+      <c r="H53" s="145" t="n"/>
+      <c r="I53" s="145" t="n"/>
+      <c r="J53" s="135">
+        <f>SUM(C51:I51)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54" ht="16.5" customHeight="1" s="77" thickBot="1">
+      <c r="A54" s="106" t="n"/>
+      <c r="B54" s="62" t="inlineStr">
         <is>
           <t>혈전용해치료비</t>
         </is>
       </c>
-      <c r="C53" s="126" t="n"/>
-      <c r="D53" s="126" t="n"/>
-      <c r="E53" s="126" t="n"/>
-      <c r="F53" s="126" t="n"/>
-      <c r="G53" s="126" t="n"/>
-      <c r="H53" s="126" t="n"/>
-      <c r="I53" s="126" t="n"/>
-      <c r="J53" s="127">
-        <f>SUM(C47:I47)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="54" ht="16.5" customHeight="1" s="77" thickBot="1">
-      <c r="A54" s="104" t="inlineStr">
+      <c r="C54" s="126" t="n"/>
+      <c r="D54" s="126" t="n"/>
+      <c r="E54" s="126" t="n"/>
+      <c r="F54" s="126" t="n"/>
+      <c r="G54" s="126" t="n"/>
+      <c r="H54" s="126" t="n"/>
+      <c r="I54" s="126" t="n"/>
+      <c r="J54" s="127">
+        <f>SUM(C48:I48)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55" ht="16.5" customHeight="1" s="77">
+      <c r="A55" s="104" t="inlineStr">
         <is>
           <t>일당</t>
         </is>
       </c>
-      <c r="B54" s="109" t="inlineStr">
+      <c r="B55" s="109" t="inlineStr">
         <is>
           <t>질병일당</t>
         </is>
       </c>
-      <c r="C54" s="132" t="n"/>
-      <c r="D54" s="132" t="n"/>
-      <c r="E54" s="132" t="n"/>
-      <c r="F54" s="132" t="n"/>
-      <c r="G54" s="132" t="n"/>
-      <c r="H54" s="132" t="n"/>
-      <c r="I54" s="132" t="n"/>
-      <c r="J54" s="133">
-        <f>SUM(#REF!)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="55" ht="16.5" customHeight="1" s="77">
-      <c r="A55" s="105" t="n"/>
-      <c r="B55" s="63" t="inlineStr">
-        <is>
-          <t>질병수술일당</t>
-        </is>
-      </c>
-      <c r="C55" s="155" t="n"/>
-      <c r="D55" s="155" t="n"/>
-      <c r="E55" s="155" t="n"/>
-      <c r="F55" s="155" t="n"/>
-      <c r="G55" s="155" t="n"/>
-      <c r="H55" s="155" t="n"/>
-      <c r="I55" s="155" t="n"/>
-      <c r="J55" s="135">
+      <c r="C55" s="132" t="n"/>
+      <c r="D55" s="132" t="n"/>
+      <c r="E55" s="132" t="n"/>
+      <c r="F55" s="132" t="n"/>
+      <c r="G55" s="132" t="n"/>
+      <c r="H55" s="132" t="n"/>
+      <c r="I55" s="132" t="n"/>
+      <c r="J55" s="133">
         <f>SUM(#REF!)</f>
         <v/>
       </c>
@@ -2628,7 +2628,7 @@
       <c r="A56" s="105" t="n"/>
       <c r="B56" s="63" t="inlineStr">
         <is>
-          <t>종합병원 질병입원일당</t>
+          <t>질병수술일당</t>
         </is>
       </c>
       <c r="C56" s="155" t="n"/>
@@ -2639,7 +2639,7 @@
       <c r="H56" s="155" t="n"/>
       <c r="I56" s="155" t="n"/>
       <c r="J56" s="135">
-        <f>SUM(C48:I48)</f>
+        <f>SUM(#REF!)</f>
         <v/>
       </c>
     </row>
@@ -2647,7 +2647,7 @@
       <c r="A57" s="105" t="n"/>
       <c r="B57" s="63" t="inlineStr">
         <is>
-          <t>종합병원 상해입원일당</t>
+          <t>종합병원 질병입원일당</t>
         </is>
       </c>
       <c r="C57" s="155" t="n"/>
@@ -2657,32 +2657,32 @@
       <c r="G57" s="155" t="n"/>
       <c r="H57" s="155" t="n"/>
       <c r="I57" s="155" t="n"/>
-      <c r="J57" s="135" t="n"/>
+      <c r="J57" s="135">
+        <f>SUM(C49:I49)</f>
+        <v/>
+      </c>
     </row>
     <row r="58" ht="16.5" customHeight="1" s="77">
       <c r="A58" s="105" t="n"/>
-      <c r="B58" s="58" t="inlineStr">
-        <is>
-          <t>상해일당</t>
-        </is>
-      </c>
-      <c r="C58" s="134" t="n"/>
-      <c r="D58" s="134" t="n"/>
-      <c r="E58" s="134" t="n"/>
-      <c r="F58" s="134" t="n"/>
-      <c r="G58" s="134" t="n"/>
-      <c r="H58" s="134" t="n"/>
-      <c r="I58" s="134" t="n"/>
-      <c r="J58" s="135">
-        <f>SUM(C49:I49)</f>
-        <v/>
-      </c>
+      <c r="B58" s="63" t="inlineStr">
+        <is>
+          <t>종합병원 상해입원일당</t>
+        </is>
+      </c>
+      <c r="C58" s="155" t="n"/>
+      <c r="D58" s="155" t="n"/>
+      <c r="E58" s="155" t="n"/>
+      <c r="F58" s="155" t="n"/>
+      <c r="G58" s="155" t="n"/>
+      <c r="H58" s="155" t="n"/>
+      <c r="I58" s="155" t="n"/>
+      <c r="J58" s="135" t="n"/>
     </row>
     <row r="59" ht="16.5" customHeight="1" s="77">
       <c r="A59" s="105" t="n"/>
       <c r="B59" s="58" t="inlineStr">
         <is>
-          <t>상해수술일당</t>
+          <t>상해일당</t>
         </is>
       </c>
       <c r="C59" s="134" t="n"/>
@@ -2692,13 +2692,16 @@
       <c r="G59" s="134" t="n"/>
       <c r="H59" s="134" t="n"/>
       <c r="I59" s="134" t="n"/>
-      <c r="J59" s="135" t="n"/>
+      <c r="J59" s="135">
+        <f>SUM(C50:I50)</f>
+        <v/>
+      </c>
     </row>
     <row r="60" ht="16.5" customHeight="1" s="77">
       <c r="A60" s="105" t="n"/>
-      <c r="B60" s="31" t="inlineStr">
-        <is>
-          <t>간병인</t>
+      <c r="B60" s="58" t="inlineStr">
+        <is>
+          <t>상해수술일당</t>
         </is>
       </c>
       <c r="C60" s="134" t="n"/>
@@ -2708,16 +2711,13 @@
       <c r="G60" s="134" t="n"/>
       <c r="H60" s="134" t="n"/>
       <c r="I60" s="134" t="n"/>
-      <c r="J60" s="135">
-        <f>SUM(C50:I50)</f>
-        <v/>
-      </c>
+      <c r="J60" s="135" t="n"/>
     </row>
     <row r="61" ht="16.5" customHeight="1" s="77">
       <c r="A61" s="105" t="n"/>
       <c r="B61" s="31" t="inlineStr">
         <is>
-          <t>간병인지원일당</t>
+          <t>간병인</t>
         </is>
       </c>
       <c r="C61" s="134" t="n"/>
@@ -2727,13 +2727,16 @@
       <c r="G61" s="134" t="n"/>
       <c r="H61" s="134" t="n"/>
       <c r="I61" s="134" t="n"/>
-      <c r="J61" s="135" t="n"/>
+      <c r="J61" s="135">
+        <f>SUM(C51:I51)</f>
+        <v/>
+      </c>
     </row>
     <row r="62" ht="16.5" customHeight="1" s="77">
       <c r="A62" s="105" t="n"/>
       <c r="B62" s="31" t="inlineStr">
         <is>
-          <t>간호통합병동</t>
+          <t>간병인지원일당</t>
         </is>
       </c>
       <c r="C62" s="134" t="n"/>
@@ -2743,16 +2746,13 @@
       <c r="G62" s="134" t="n"/>
       <c r="H62" s="134" t="n"/>
       <c r="I62" s="134" t="n"/>
-      <c r="J62" s="135">
-        <f>SUM(C53:I53)</f>
-        <v/>
-      </c>
+      <c r="J62" s="135" t="n"/>
     </row>
     <row r="63" ht="16.5" customHeight="1" s="77">
       <c r="A63" s="105" t="n"/>
-      <c r="B63" s="64" t="inlineStr">
-        <is>
-          <t>1인실 종합병원</t>
+      <c r="B63" s="31" t="inlineStr">
+        <is>
+          <t>간호통합병동</t>
         </is>
       </c>
       <c r="C63" s="134" t="n"/>
@@ -2767,11 +2767,11 @@
         <v/>
       </c>
     </row>
-    <row r="64" ht="17.25" customHeight="1" s="77">
+    <row r="64" ht="16.5" customHeight="1" s="77">
       <c r="A64" s="105" t="n"/>
       <c r="B64" s="64" t="inlineStr">
         <is>
-          <t>1인실 상급병원</t>
+          <t>1인실 종합병원</t>
         </is>
       </c>
       <c r="C64" s="134" t="n"/>
@@ -2788,9 +2788,9 @@
     </row>
     <row r="65" ht="17.25" customHeight="1" s="77">
       <c r="A65" s="105" t="n"/>
-      <c r="B65" s="31" t="inlineStr">
-        <is>
-          <t>질병중환자실</t>
+      <c r="B65" s="64" t="inlineStr">
+        <is>
+          <t>1인실 상급병원</t>
         </is>
       </c>
       <c r="C65" s="134" t="n"/>
@@ -2805,88 +2805,91 @@
         <v/>
       </c>
     </row>
-    <row r="66" ht="16.5" customHeight="1" s="77" thickBot="1">
-      <c r="A66" s="106" t="n"/>
-      <c r="B66" s="25" t="inlineStr">
+    <row r="66" ht="17.25" customHeight="1" s="77" thickBot="1">
+      <c r="A66" s="105" t="n"/>
+      <c r="B66" s="31" t="inlineStr">
+        <is>
+          <t>질병중환자실</t>
+        </is>
+      </c>
+      <c r="C66" s="134" t="n"/>
+      <c r="D66" s="134" t="n"/>
+      <c r="E66" s="134" t="n"/>
+      <c r="F66" s="134" t="n"/>
+      <c r="G66" s="134" t="n"/>
+      <c r="H66" s="134" t="n"/>
+      <c r="I66" s="134" t="n"/>
+      <c r="J66" s="135">
+        <f>SUM(C57:I57)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67" ht="16.5" customHeight="1" s="77">
+      <c r="A67" s="106" t="n"/>
+      <c r="B67" s="25" t="inlineStr">
         <is>
           <t>상해중환자실</t>
         </is>
       </c>
-      <c r="C66" s="130" t="n"/>
-      <c r="D66" s="130" t="n"/>
-      <c r="E66" s="130" t="n"/>
-      <c r="F66" s="130" t="n"/>
-      <c r="G66" s="130" t="n"/>
-      <c r="H66" s="130" t="n"/>
-      <c r="I66" s="130" t="n"/>
-      <c r="J66" s="131">
-        <f>SUM(C57:I57)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="67" ht="16.5" customHeight="1" s="77">
-      <c r="A67" s="104" t="inlineStr">
+      <c r="C67" s="130" t="n"/>
+      <c r="D67" s="130" t="n"/>
+      <c r="E67" s="130" t="n"/>
+      <c r="F67" s="130" t="n"/>
+      <c r="G67" s="130" t="n"/>
+      <c r="H67" s="130" t="n"/>
+      <c r="I67" s="130" t="n"/>
+      <c r="J67" s="131">
+        <f>SUM(C58:I58)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68" ht="16.5" customHeight="1" s="77">
+      <c r="A68" s="104" t="inlineStr">
         <is>
           <t>수술</t>
         </is>
       </c>
-      <c r="B67" s="109" t="inlineStr">
+      <c r="B68" s="109" t="inlineStr">
         <is>
           <t>상해수술비</t>
         </is>
       </c>
-      <c r="C67" s="132" t="n"/>
-      <c r="D67" s="132" t="n"/>
-      <c r="E67" s="132" t="n"/>
-      <c r="F67" s="132" t="n"/>
-      <c r="G67" s="132" t="n"/>
-      <c r="H67" s="132" t="n"/>
-      <c r="I67" s="132" t="n"/>
-      <c r="J67" s="133">
-        <f>SUM(C58:I58)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="68" ht="16.5" customHeight="1" s="77">
-      <c r="A68" s="105" t="n"/>
-      <c r="B68" s="63" t="inlineStr">
-        <is>
-          <t>중대한상해수술비</t>
-        </is>
-      </c>
-      <c r="C68" s="155" t="n"/>
-      <c r="D68" s="155" t="n"/>
-      <c r="E68" s="155" t="n"/>
-      <c r="F68" s="155" t="n"/>
-      <c r="G68" s="155" t="n"/>
-      <c r="H68" s="155" t="n"/>
-      <c r="I68" s="155" t="n"/>
-      <c r="J68" s="135">
+      <c r="C68" s="132" t="n"/>
+      <c r="D68" s="132" t="n"/>
+      <c r="E68" s="132" t="n"/>
+      <c r="F68" s="132" t="n"/>
+      <c r="G68" s="132" t="n"/>
+      <c r="H68" s="132" t="n"/>
+      <c r="I68" s="132" t="n"/>
+      <c r="J68" s="133">
         <f>SUM(C59:I59)</f>
         <v/>
       </c>
     </row>
     <row r="69" ht="16.5" customHeight="1" s="77">
       <c r="A69" s="105" t="n"/>
-      <c r="B69" s="58" t="inlineStr">
-        <is>
-          <t>상해 종수술비(1-3종)</t>
+      <c r="B69" s="63" t="inlineStr">
+        <is>
+          <t>중대한상해수술비</t>
         </is>
       </c>
       <c r="C69" s="155" t="n"/>
       <c r="D69" s="155" t="n"/>
       <c r="E69" s="155" t="n"/>
-      <c r="F69" s="156" t="n"/>
+      <c r="F69" s="155" t="n"/>
       <c r="G69" s="155" t="n"/>
       <c r="H69" s="155" t="n"/>
       <c r="I69" s="155" t="n"/>
-      <c r="J69" s="135" t="n"/>
-    </row>
-    <row r="70" ht="17.25" customHeight="1" s="77">
+      <c r="J69" s="135">
+        <f>SUM(C60:I60)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70" ht="16.5" customHeight="1" s="77">
       <c r="A70" s="105" t="n"/>
       <c r="B70" s="58" t="inlineStr">
         <is>
-          <t>상해 종수술비(1-5종)</t>
+          <t>상해 종수술비(1-3종)</t>
         </is>
       </c>
       <c r="C70" s="155" t="n"/>
@@ -2896,17 +2899,13 @@
       <c r="G70" s="155" t="n"/>
       <c r="H70" s="155" t="n"/>
       <c r="I70" s="155" t="n"/>
-      <c r="J70" s="135" t="inlineStr">
-        <is>
-          <t>/ / / / /</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="16.5" customHeight="1" s="77">
+      <c r="J70" s="135" t="n"/>
+    </row>
+    <row r="71" ht="17.25" customHeight="1" s="77">
       <c r="A71" s="105" t="n"/>
       <c r="B71" s="58" t="inlineStr">
         <is>
-          <t>상해 종수술비(1-8종)</t>
+          <t>상해 종수술비(1-5종)</t>
         </is>
       </c>
       <c r="C71" s="155" t="n"/>
@@ -2916,32 +2915,33 @@
       <c r="G71" s="155" t="n"/>
       <c r="H71" s="155" t="n"/>
       <c r="I71" s="155" t="n"/>
-      <c r="J71" s="135" t="n"/>
+      <c r="J71" s="135" t="inlineStr">
+        <is>
+          <t>/ / / / /</t>
+        </is>
+      </c>
     </row>
     <row r="72" ht="16.5" customHeight="1" s="77">
       <c r="A72" s="105" t="n"/>
       <c r="B72" s="58" t="inlineStr">
         <is>
-          <t>창상봉합술</t>
-        </is>
-      </c>
-      <c r="C72" s="134" t="n"/>
-      <c r="D72" s="134" t="n"/>
-      <c r="E72" s="134" t="n"/>
-      <c r="F72" s="157" t="n"/>
-      <c r="G72" s="134" t="n"/>
-      <c r="H72" s="134" t="n"/>
-      <c r="I72" s="134" t="n"/>
-      <c r="J72" s="135">
-        <f>SUM(C61:I61)</f>
-        <v/>
-      </c>
+          <t>상해 종수술비(1-8종)</t>
+        </is>
+      </c>
+      <c r="C72" s="155" t="n"/>
+      <c r="D72" s="155" t="n"/>
+      <c r="E72" s="155" t="n"/>
+      <c r="F72" s="156" t="n"/>
+      <c r="G72" s="155" t="n"/>
+      <c r="H72" s="155" t="n"/>
+      <c r="I72" s="155" t="n"/>
+      <c r="J72" s="135" t="n"/>
     </row>
     <row r="73" ht="16.5" customHeight="1" s="77">
       <c r="A73" s="105" t="n"/>
       <c r="B73" s="58" t="inlineStr">
         <is>
-          <t>골절수술비</t>
+          <t>창상봉합술</t>
         </is>
       </c>
       <c r="C73" s="134" t="n"/>
@@ -2958,9 +2958,9 @@
     </row>
     <row r="74" ht="16.5" customHeight="1" s="77">
       <c r="A74" s="105" t="n"/>
-      <c r="B74" s="65" t="inlineStr">
-        <is>
-          <t>5대골절수술비</t>
+      <c r="B74" s="58" t="inlineStr">
+        <is>
+          <t>골절수술비</t>
         </is>
       </c>
       <c r="C74" s="134" t="n"/>
@@ -2977,63 +2977,66 @@
     </row>
     <row r="75" ht="16.5" customHeight="1" s="77" thickBot="1">
       <c r="A75" s="105" t="n"/>
-      <c r="B75" s="56" t="inlineStr">
-        <is>
-          <t>화상수술비</t>
-        </is>
-      </c>
-      <c r="C75" s="130" t="n"/>
-      <c r="D75" s="130" t="n"/>
-      <c r="E75" s="130" t="n"/>
-      <c r="F75" s="158" t="n"/>
-      <c r="G75" s="130" t="n"/>
-      <c r="H75" s="130" t="n"/>
-      <c r="I75" s="130" t="n"/>
-      <c r="J75" s="131">
+      <c r="B75" s="65" t="inlineStr">
+        <is>
+          <t>5대골절수술비</t>
+        </is>
+      </c>
+      <c r="C75" s="134" t="n"/>
+      <c r="D75" s="134" t="n"/>
+      <c r="E75" s="134" t="n"/>
+      <c r="F75" s="157" t="n"/>
+      <c r="G75" s="134" t="n"/>
+      <c r="H75" s="134" t="n"/>
+      <c r="I75" s="134" t="n"/>
+      <c r="J75" s="135">
         <f>SUM(C64:I64)</f>
         <v/>
       </c>
     </row>
     <row r="76" ht="16.5" customHeight="1" s="77">
       <c r="A76" s="105" t="n"/>
-      <c r="B76" s="63" t="inlineStr">
-        <is>
-          <t>질병수술비</t>
-        </is>
-      </c>
-      <c r="C76" s="155" t="n"/>
-      <c r="D76" s="155" t="n"/>
-      <c r="E76" s="155" t="n"/>
-      <c r="F76" s="159" t="n"/>
-      <c r="G76" s="155" t="n"/>
-      <c r="H76" s="155" t="n"/>
-      <c r="I76" s="160" t="n"/>
-      <c r="J76" s="129">
+      <c r="B76" s="56" t="inlineStr">
+        <is>
+          <t>화상수술비</t>
+        </is>
+      </c>
+      <c r="C76" s="130" t="n"/>
+      <c r="D76" s="130" t="n"/>
+      <c r="E76" s="130" t="n"/>
+      <c r="F76" s="158" t="n"/>
+      <c r="G76" s="130" t="n"/>
+      <c r="H76" s="130" t="n"/>
+      <c r="I76" s="130" t="n"/>
+      <c r="J76" s="131">
         <f>SUM(C65:I65)</f>
         <v/>
       </c>
     </row>
     <row r="77" ht="16.5" customHeight="1" s="77">
       <c r="A77" s="105" t="n"/>
-      <c r="B77" s="58" t="inlineStr">
-        <is>
-          <t>질병 종수술비(1-3종)</t>
-        </is>
-      </c>
-      <c r="C77" s="134" t="n"/>
-      <c r="D77" s="134" t="n"/>
-      <c r="E77" s="134" t="n"/>
-      <c r="F77" s="161" t="n"/>
-      <c r="G77" s="134" t="n"/>
-      <c r="H77" s="134" t="n"/>
-      <c r="I77" s="134" t="n"/>
-      <c r="J77" s="135" t="n"/>
-    </row>
-    <row r="78" ht="17.25" customHeight="1" s="77">
+      <c r="B77" s="63" t="inlineStr">
+        <is>
+          <t>질병수술비</t>
+        </is>
+      </c>
+      <c r="C77" s="155" t="n"/>
+      <c r="D77" s="155" t="n"/>
+      <c r="E77" s="155" t="n"/>
+      <c r="F77" s="159" t="n"/>
+      <c r="G77" s="155" t="n"/>
+      <c r="H77" s="155" t="n"/>
+      <c r="I77" s="160" t="n"/>
+      <c r="J77" s="129">
+        <f>SUM(C66:I66)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78" ht="16.5" customHeight="1" s="77">
       <c r="A78" s="105" t="n"/>
       <c r="B78" s="58" t="inlineStr">
         <is>
-          <t>질병 종수술비(1-5종)</t>
+          <t>질병 종수술비(1-3종)</t>
         </is>
       </c>
       <c r="C78" s="134" t="n"/>
@@ -3043,17 +3046,13 @@
       <c r="G78" s="134" t="n"/>
       <c r="H78" s="134" t="n"/>
       <c r="I78" s="134" t="n"/>
-      <c r="J78" s="135" t="inlineStr">
-        <is>
-          <t>/ / / / /</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="16.5" customHeight="1" s="77">
+      <c r="J78" s="135" t="n"/>
+    </row>
+    <row r="79" ht="17.25" customHeight="1" s="77">
       <c r="A79" s="105" t="n"/>
       <c r="B79" s="58" t="inlineStr">
         <is>
-          <t>질병 종수술비(1-8종)</t>
+          <t>질병 종수술비(1-5종)</t>
         </is>
       </c>
       <c r="C79" s="134" t="n"/>
@@ -3063,32 +3062,33 @@
       <c r="G79" s="134" t="n"/>
       <c r="H79" s="134" t="n"/>
       <c r="I79" s="134" t="n"/>
-      <c r="J79" s="135" t="n"/>
+      <c r="J79" s="135" t="inlineStr">
+        <is>
+          <t>/ / / / /</t>
+        </is>
+      </c>
     </row>
     <row r="80" ht="16.5" customHeight="1" s="77">
       <c r="A80" s="105" t="n"/>
-      <c r="B80" s="67" t="inlineStr">
-        <is>
-          <t>뇌혈관수술비</t>
-        </is>
-      </c>
-      <c r="C80" s="162" t="n"/>
-      <c r="D80" s="162" t="n"/>
-      <c r="E80" s="162" t="n"/>
-      <c r="F80" s="162" t="n"/>
-      <c r="G80" s="162" t="n"/>
-      <c r="H80" s="162" t="n"/>
-      <c r="I80" s="162" t="n"/>
-      <c r="J80" s="135">
-        <f>SUM(C67:I67)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="81" ht="17.25" customHeight="1" s="77">
+      <c r="B80" s="58" t="inlineStr">
+        <is>
+          <t>질병 종수술비(1-8종)</t>
+        </is>
+      </c>
+      <c r="C80" s="134" t="n"/>
+      <c r="D80" s="134" t="n"/>
+      <c r="E80" s="134" t="n"/>
+      <c r="F80" s="161" t="n"/>
+      <c r="G80" s="134" t="n"/>
+      <c r="H80" s="134" t="n"/>
+      <c r="I80" s="134" t="n"/>
+      <c r="J80" s="135" t="n"/>
+    </row>
+    <row r="81" ht="16.5" customHeight="1" s="77">
       <c r="A81" s="105" t="n"/>
       <c r="B81" s="67" t="inlineStr">
         <is>
-          <t>허혈성수술비</t>
+          <t>뇌혈관수술비</t>
         </is>
       </c>
       <c r="C81" s="162" t="n"/>
@@ -3107,7 +3107,7 @@
       <c r="A82" s="105" t="n"/>
       <c r="B82" s="67" t="inlineStr">
         <is>
-          <t>심장수술비</t>
+          <t>허혈성수술비</t>
         </is>
       </c>
       <c r="C82" s="162" t="n"/>
@@ -3124,9 +3124,9 @@
     </row>
     <row r="83" ht="17.25" customHeight="1" s="77" thickBot="1">
       <c r="A83" s="105" t="n"/>
-      <c r="B83" s="59" t="inlineStr">
-        <is>
-          <t>n대수술비</t>
+      <c r="B83" s="67" t="inlineStr">
+        <is>
+          <t>심장수술비</t>
         </is>
       </c>
       <c r="C83" s="162" t="n"/>
@@ -3136,96 +3136,96 @@
       <c r="G83" s="162" t="n"/>
       <c r="H83" s="162" t="n"/>
       <c r="I83" s="162" t="n"/>
-      <c r="J83" s="163">
+      <c r="J83" s="135">
         <f>SUM(C70:I70)</f>
         <v/>
       </c>
     </row>
-    <row r="84" ht="16.5" customHeight="1" s="77">
+    <row r="84" ht="17.25" customHeight="1" s="77">
       <c r="A84" s="105" t="n"/>
-      <c r="B84" s="68" t="inlineStr">
+      <c r="B84" s="59" t="inlineStr">
+        <is>
+          <t>n대수술비</t>
+        </is>
+      </c>
+      <c r="C84" s="162" t="n"/>
+      <c r="D84" s="162" t="n"/>
+      <c r="E84" s="162" t="n"/>
+      <c r="F84" s="162" t="n"/>
+      <c r="G84" s="162" t="n"/>
+      <c r="H84" s="162" t="n"/>
+      <c r="I84" s="162" t="n"/>
+      <c r="J84" s="163">
+        <f>SUM(C71:I71)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85" ht="16.5" customHeight="1" s="77" thickBot="1">
+      <c r="A85" s="105" t="n"/>
+      <c r="B85" s="68" t="inlineStr">
         <is>
           <t>5대기관 수술비 관혈</t>
         </is>
       </c>
-      <c r="C84" s="136" t="n"/>
-      <c r="D84" s="136" t="n"/>
-      <c r="E84" s="136" t="n"/>
-      <c r="F84" s="136" t="n"/>
-      <c r="G84" s="136" t="n"/>
-      <c r="H84" s="136" t="n"/>
-      <c r="I84" s="136" t="n"/>
-      <c r="J84" s="133">
-        <f>SUM(C71:I71)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="85" ht="17.25" customHeight="1" s="77" thickBot="1">
-      <c r="A85" s="106" t="n"/>
-      <c r="B85" s="69" t="inlineStr">
+      <c r="C85" s="136" t="n"/>
+      <c r="D85" s="136" t="n"/>
+      <c r="E85" s="136" t="n"/>
+      <c r="F85" s="136" t="n"/>
+      <c r="G85" s="136" t="n"/>
+      <c r="H85" s="136" t="n"/>
+      <c r="I85" s="136" t="n"/>
+      <c r="J85" s="133">
+        <f>SUM(C72:I72)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86" ht="17.25" customHeight="1" s="77" thickBot="1">
+      <c r="A86" s="106" t="n"/>
+      <c r="B86" s="69" t="inlineStr">
         <is>
           <t>5대기관 수술비 비관혈</t>
         </is>
       </c>
-      <c r="C85" s="130" t="n"/>
-      <c r="D85" s="130" t="n"/>
-      <c r="E85" s="130" t="n"/>
-      <c r="F85" s="130" t="n"/>
-      <c r="G85" s="130" t="n"/>
-      <c r="H85" s="130" t="n"/>
-      <c r="I85" s="130" t="n"/>
-      <c r="J85" s="131">
-        <f>SUM(C72:I72)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="86" ht="16.5" customHeight="1" s="77" thickBot="1">
-      <c r="A86" s="104" t="inlineStr">
+      <c r="C86" s="130" t="n"/>
+      <c r="D86" s="130" t="n"/>
+      <c r="E86" s="130" t="n"/>
+      <c r="F86" s="130" t="n"/>
+      <c r="G86" s="130" t="n"/>
+      <c r="H86" s="130" t="n"/>
+      <c r="I86" s="130" t="n"/>
+      <c r="J86" s="131">
+        <f>SUM(C73:I73)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="87" ht="16.5" customHeight="1" s="77">
+      <c r="A87" s="104" t="inlineStr">
         <is>
           <t>운전</t>
         </is>
       </c>
-      <c r="B86" s="28" t="inlineStr">
+      <c r="B87" s="28" t="inlineStr">
         <is>
           <t>대인</t>
         </is>
       </c>
-      <c r="C86" s="115" t="n"/>
-      <c r="D86" s="115" t="n"/>
-      <c r="E86" s="115" t="n"/>
-      <c r="F86" s="115" t="n"/>
-      <c r="G86" s="115" t="n"/>
-      <c r="H86" s="115" t="n"/>
-      <c r="I86" s="115" t="n"/>
-      <c r="J86" s="133">
-        <f>SUM(C73:I73)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="87" ht="17.25" customHeight="1" s="77">
-      <c r="A87" s="105" t="n"/>
-      <c r="B87" s="31" t="inlineStr">
-        <is>
-          <t>대물</t>
-        </is>
-      </c>
-      <c r="C87" s="145" t="n"/>
-      <c r="D87" s="145" t="n"/>
-      <c r="E87" s="145" t="n"/>
-      <c r="F87" s="145" t="n"/>
-      <c r="G87" s="145" t="n"/>
-      <c r="H87" s="145" t="n"/>
-      <c r="I87" s="145" t="n"/>
-      <c r="J87" s="135">
+      <c r="C87" s="115" t="n"/>
+      <c r="D87" s="115" t="n"/>
+      <c r="E87" s="115" t="n"/>
+      <c r="F87" s="115" t="n"/>
+      <c r="G87" s="115" t="n"/>
+      <c r="H87" s="115" t="n"/>
+      <c r="I87" s="115" t="n"/>
+      <c r="J87" s="133">
         <f>SUM(C74:I74)</f>
         <v/>
       </c>
     </row>
-    <row r="88" ht="16.5" customHeight="1" s="77">
+    <row r="88" ht="17.25" customHeight="1" s="77">
       <c r="A88" s="105" t="n"/>
       <c r="B88" s="31" t="inlineStr">
         <is>
-          <t>합의금</t>
+          <t>대물</t>
         </is>
       </c>
       <c r="C88" s="145" t="n"/>
@@ -3242,9 +3242,9 @@
     </row>
     <row r="89" ht="16.5" customHeight="1" s="77">
       <c r="A89" s="105" t="n"/>
-      <c r="B89" s="64" t="inlineStr">
-        <is>
-          <t>6주미만</t>
+      <c r="B89" s="31" t="inlineStr">
+        <is>
+          <t>합의금</t>
         </is>
       </c>
       <c r="C89" s="145" t="n"/>
@@ -3259,11 +3259,11 @@
         <v/>
       </c>
     </row>
-    <row r="90" ht="17.25" customHeight="1" s="77">
+    <row r="90" ht="16.5" customHeight="1" s="77">
       <c r="A90" s="105" t="n"/>
-      <c r="B90" s="31" t="inlineStr">
-        <is>
-          <t>변호사</t>
+      <c r="B90" s="64" t="inlineStr">
+        <is>
+          <t>6주미만</t>
         </is>
       </c>
       <c r="C90" s="145" t="n"/>
@@ -3279,104 +3279,100 @@
       </c>
     </row>
     <row r="91" ht="17.25" customHeight="1" s="77">
-      <c r="A91" s="106" t="n"/>
-      <c r="B91" s="25" t="inlineStr">
+      <c r="A91" s="105" t="n"/>
+      <c r="B91" s="31" t="inlineStr">
+        <is>
+          <t>변호사</t>
+        </is>
+      </c>
+      <c r="C91" s="145" t="n"/>
+      <c r="D91" s="145" t="n"/>
+      <c r="E91" s="145" t="n"/>
+      <c r="F91" s="145" t="n"/>
+      <c r="G91" s="145" t="n"/>
+      <c r="H91" s="145" t="n"/>
+      <c r="I91" s="145" t="n"/>
+      <c r="J91" s="135">
+        <f>SUM(C78:I78)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="92" ht="17.25" customHeight="1" s="77">
+      <c r="A92" s="106" t="n"/>
+      <c r="B92" s="25" t="inlineStr">
         <is>
           <t>자부상</t>
         </is>
       </c>
-      <c r="C91" s="164" t="n"/>
-      <c r="D91" s="164" t="n"/>
-      <c r="E91" s="164" t="n"/>
-      <c r="F91" s="164" t="n"/>
-      <c r="G91" s="164" t="n"/>
-      <c r="H91" s="164" t="n"/>
-      <c r="I91" s="164" t="n"/>
-      <c r="J91" s="131">
-        <f>SUM(C78:I78)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="92" ht="16.5" customHeight="1" s="77">
-      <c r="A92" s="104" t="inlineStr">
+      <c r="C92" s="164" t="n"/>
+      <c r="D92" s="164" t="n"/>
+      <c r="E92" s="164" t="n"/>
+      <c r="F92" s="164" t="n"/>
+      <c r="G92" s="164" t="n"/>
+      <c r="H92" s="164" t="n"/>
+      <c r="I92" s="164" t="n"/>
+      <c r="J92" s="131">
+        <f>SUM(C79:I79)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="93" ht="16.5" customHeight="1" s="77">
+      <c r="A93" s="104" t="inlineStr">
         <is>
           <t>골절</t>
         </is>
       </c>
-      <c r="B92" s="63" t="inlineStr">
+      <c r="B93" s="63" t="inlineStr">
         <is>
           <t>골절(치아파절포함)</t>
         </is>
       </c>
-      <c r="C92" s="155" t="n"/>
-      <c r="D92" s="155" t="n"/>
-      <c r="E92" s="155" t="n"/>
-      <c r="F92" s="155" t="n"/>
-      <c r="G92" s="155" t="n"/>
-      <c r="H92" s="155" t="n"/>
-      <c r="I92" s="155" t="n"/>
-      <c r="J92" s="129">
-        <f>SUM(C79:I79)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="93" ht="16.5" customHeight="1" s="77">
-      <c r="A93" s="105" t="n"/>
-      <c r="B93" s="58" t="inlineStr">
+      <c r="C93" s="155" t="n"/>
+      <c r="D93" s="155" t="n"/>
+      <c r="E93" s="155" t="n"/>
+      <c r="F93" s="155" t="n"/>
+      <c r="G93" s="155" t="n"/>
+      <c r="H93" s="155" t="n"/>
+      <c r="I93" s="155" t="n"/>
+      <c r="J93" s="129">
+        <f>SUM(C80:I80)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="94" ht="16.5" customHeight="1" s="77">
+      <c r="A94" s="105" t="n"/>
+      <c r="B94" s="58" t="inlineStr">
         <is>
           <t>골절(치아파절제외)</t>
         </is>
       </c>
-      <c r="C93" s="134" t="n"/>
-      <c r="D93" s="134" t="n"/>
-      <c r="E93" s="134" t="n"/>
-      <c r="F93" s="134" t="n"/>
-      <c r="G93" s="134" t="n"/>
-      <c r="H93" s="134" t="n"/>
-      <c r="I93" s="134" t="n"/>
-      <c r="J93" s="135">
-        <f>SUM(C80:I80)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="94" ht="16.5" customHeight="1" s="77">
-      <c r="A94" s="106" t="n"/>
-      <c r="B94" s="69" t="inlineStr">
+      <c r="C94" s="134" t="n"/>
+      <c r="D94" s="134" t="n"/>
+      <c r="E94" s="134" t="n"/>
+      <c r="F94" s="134" t="n"/>
+      <c r="G94" s="134" t="n"/>
+      <c r="H94" s="134" t="n"/>
+      <c r="I94" s="134" t="n"/>
+      <c r="J94" s="135">
+        <f>SUM(C81:I81)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="95" ht="16.5" customHeight="1" s="77">
+      <c r="A95" s="106" t="n"/>
+      <c r="B95" s="69" t="inlineStr">
         <is>
           <t>5대골절진단비</t>
         </is>
       </c>
-      <c r="C94" s="130" t="n"/>
-      <c r="D94" s="130" t="n"/>
-      <c r="E94" s="130" t="n"/>
-      <c r="F94" s="130" t="n"/>
-      <c r="G94" s="130" t="n"/>
-      <c r="H94" s="130" t="n"/>
-      <c r="I94" s="130" t="n"/>
-      <c r="J94" s="131">
-        <f>SUM(C81:I81)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="95" ht="16.5" customHeight="1" s="77">
-      <c r="A95" s="104" t="inlineStr">
-        <is>
-          <t>응급실</t>
-        </is>
-      </c>
-      <c r="B95" s="62" t="inlineStr">
-        <is>
-          <t>응급실(응급)</t>
-        </is>
-      </c>
-      <c r="C95" s="126" t="n"/>
-      <c r="D95" s="126" t="n"/>
-      <c r="E95" s="126" t="n"/>
-      <c r="F95" s="126" t="n"/>
-      <c r="G95" s="126" t="n"/>
-      <c r="H95" s="126" t="n"/>
-      <c r="I95" s="126" t="n"/>
-      <c r="J95" s="127">
+      <c r="C95" s="130" t="n"/>
+      <c r="D95" s="130" t="n"/>
+      <c r="E95" s="130" t="n"/>
+      <c r="F95" s="130" t="n"/>
+      <c r="G95" s="130" t="n"/>
+      <c r="H95" s="130" t="n"/>
+      <c r="I95" s="130" t="n"/>
+      <c r="J95" s="131">
         <f>SUM(C82:I82)</f>
         <v/>
       </c>
@@ -3384,145 +3380,149 @@
     <row r="96" ht="16.5" customHeight="1" s="77">
       <c r="A96" s="104" t="inlineStr">
         <is>
-          <t>독감</t>
-        </is>
-      </c>
-      <c r="B96" s="34" t="inlineStr">
-        <is>
-          <t>독감</t>
-        </is>
-      </c>
-      <c r="C96" s="136" t="n"/>
-      <c r="D96" s="136" t="n"/>
-      <c r="E96" s="136" t="n"/>
-      <c r="F96" s="136" t="n"/>
-      <c r="G96" s="136" t="n"/>
-      <c r="H96" s="136" t="n"/>
-      <c r="I96" s="136" t="n"/>
-      <c r="J96" s="137" t="n"/>
+          <t>응급실</t>
+        </is>
+      </c>
+      <c r="B96" s="62" t="inlineStr">
+        <is>
+          <t>응급실(응급)</t>
+        </is>
+      </c>
+      <c r="C96" s="126" t="n"/>
+      <c r="D96" s="126" t="n"/>
+      <c r="E96" s="126" t="n"/>
+      <c r="F96" s="126" t="n"/>
+      <c r="G96" s="126" t="n"/>
+      <c r="H96" s="126" t="n"/>
+      <c r="I96" s="126" t="n"/>
+      <c r="J96" s="127">
+        <f>SUM(C83:I83)</f>
+        <v/>
+      </c>
     </row>
     <row r="97" ht="16.5" customHeight="1" s="77">
       <c r="A97" s="104" t="inlineStr">
         <is>
+          <t>독감</t>
+        </is>
+      </c>
+      <c r="B97" s="34" t="inlineStr">
+        <is>
+          <t>독감</t>
+        </is>
+      </c>
+      <c r="C97" s="136" t="n"/>
+      <c r="D97" s="136" t="n"/>
+      <c r="E97" s="136" t="n"/>
+      <c r="F97" s="136" t="n"/>
+      <c r="G97" s="136" t="n"/>
+      <c r="H97" s="136" t="n"/>
+      <c r="I97" s="136" t="n"/>
+      <c r="J97" s="137" t="n"/>
+    </row>
+    <row r="98" ht="16.5" customHeight="1" s="77">
+      <c r="A98" s="104" t="inlineStr">
+        <is>
           <t>화상</t>
         </is>
       </c>
-      <c r="B97" s="28" t="inlineStr">
+      <c r="B98" s="28" t="inlineStr">
         <is>
           <t>화상진단비</t>
         </is>
       </c>
-      <c r="C97" s="132" t="n"/>
-      <c r="D97" s="132" t="n"/>
-      <c r="E97" s="132" t="n"/>
-      <c r="F97" s="132" t="n"/>
-      <c r="G97" s="132" t="n"/>
-      <c r="H97" s="132" t="n"/>
-      <c r="I97" s="132" t="n"/>
-      <c r="J97" s="133">
-        <f>SUM(C84:I84)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="98" ht="16.5" customHeight="1" s="77">
-      <c r="A98" s="106" t="n"/>
-      <c r="B98" s="25" t="inlineStr">
+      <c r="C98" s="132" t="n"/>
+      <c r="D98" s="132" t="n"/>
+      <c r="E98" s="132" t="n"/>
+      <c r="F98" s="132" t="n"/>
+      <c r="G98" s="132" t="n"/>
+      <c r="H98" s="132" t="n"/>
+      <c r="I98" s="132" t="n"/>
+      <c r="J98" s="133">
+        <f>SUM(C85:I85)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="99" ht="16.5" customHeight="1" s="77">
+      <c r="A99" s="106" t="n"/>
+      <c r="B99" s="25" t="inlineStr">
         <is>
           <t>중증화상진단비</t>
         </is>
       </c>
-      <c r="C98" s="130" t="n"/>
-      <c r="D98" s="130" t="n"/>
-      <c r="E98" s="130" t="n"/>
-      <c r="F98" s="130" t="n"/>
-      <c r="G98" s="130" t="n"/>
-      <c r="H98" s="130" t="n"/>
-      <c r="I98" s="130" t="n"/>
-      <c r="J98" s="131">
-        <f>SUM(C85:I85)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="99" ht="16.5" customHeight="1" s="77">
-      <c r="A99" s="104" t="inlineStr">
+      <c r="C99" s="130" t="n"/>
+      <c r="D99" s="130" t="n"/>
+      <c r="E99" s="130" t="n"/>
+      <c r="F99" s="130" t="n"/>
+      <c r="G99" s="130" t="n"/>
+      <c r="H99" s="130" t="n"/>
+      <c r="I99" s="130" t="n"/>
+      <c r="J99" s="131">
+        <f>SUM(C86:I86)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="100" ht="16.5" customHeight="1" s="77">
+      <c r="A100" s="104" t="inlineStr">
         <is>
           <t>깁스</t>
         </is>
       </c>
-      <c r="B99" s="109" t="inlineStr">
+      <c r="B100" s="109" t="inlineStr">
         <is>
           <t>반깁스</t>
         </is>
       </c>
-      <c r="C99" s="132" t="n"/>
-      <c r="D99" s="132" t="n"/>
-      <c r="E99" s="132" t="n"/>
-      <c r="F99" s="132" t="n"/>
-      <c r="G99" s="132" t="n"/>
-      <c r="H99" s="132" t="n"/>
-      <c r="I99" s="132" t="n"/>
-      <c r="J99" s="133">
-        <f>SUM(C86:I86)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="100" ht="16.5" customHeight="1" s="77">
-      <c r="A100" s="106" t="n"/>
-      <c r="B100" s="56" t="inlineStr">
+      <c r="C100" s="132" t="n"/>
+      <c r="D100" s="132" t="n"/>
+      <c r="E100" s="132" t="n"/>
+      <c r="F100" s="132" t="n"/>
+      <c r="G100" s="132" t="n"/>
+      <c r="H100" s="132" t="n"/>
+      <c r="I100" s="132" t="n"/>
+      <c r="J100" s="133">
+        <f>SUM(C87:I87)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="101" ht="16.5" customHeight="1" s="77">
+      <c r="A101" s="106" t="n"/>
+      <c r="B101" s="56" t="inlineStr">
         <is>
           <t>깁스진단비</t>
         </is>
       </c>
-      <c r="C100" s="130" t="n"/>
-      <c r="D100" s="130" t="n"/>
-      <c r="E100" s="130" t="n"/>
-      <c r="F100" s="130" t="n"/>
-      <c r="G100" s="130" t="n"/>
-      <c r="H100" s="130" t="n"/>
-      <c r="I100" s="130" t="n"/>
-      <c r="J100" s="131">
-        <f>SUM(C87:I87)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="101" ht="16.5" customHeight="1" s="77">
-      <c r="A101" s="104" t="inlineStr">
+      <c r="C101" s="130" t="n"/>
+      <c r="D101" s="130" t="n"/>
+      <c r="E101" s="130" t="n"/>
+      <c r="F101" s="130" t="n"/>
+      <c r="G101" s="130" t="n"/>
+      <c r="H101" s="130" t="n"/>
+      <c r="I101" s="130" t="n"/>
+      <c r="J101" s="131">
+        <f>SUM(C88:I88)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="102" ht="16.5" customHeight="1" s="77">
+      <c r="A102" s="104" t="inlineStr">
         <is>
           <t>실손</t>
         </is>
       </c>
-      <c r="B101" s="109" t="inlineStr">
+      <c r="B102" s="109" t="inlineStr">
         <is>
           <t>입원</t>
         </is>
       </c>
-      <c r="C101" s="165" t="n"/>
-      <c r="D101" s="165" t="n"/>
-      <c r="E101" s="165" t="n"/>
-      <c r="F101" s="165" t="n"/>
-      <c r="G101" s="165" t="n"/>
-      <c r="H101" s="165" t="n"/>
-      <c r="I101" s="165" t="n"/>
-      <c r="J101" s="133">
-        <f>SUM(C88:I88)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="102" ht="16.5" customHeight="1" s="77">
-      <c r="A102" s="105" t="n"/>
-      <c r="B102" s="58" t="inlineStr">
-        <is>
-          <t>통원</t>
-        </is>
-      </c>
-      <c r="C102" s="166" t="n"/>
-      <c r="D102" s="166" t="n"/>
-      <c r="E102" s="166" t="n"/>
-      <c r="F102" s="166" t="n"/>
-      <c r="G102" s="166" t="n"/>
-      <c r="H102" s="166" t="n"/>
-      <c r="I102" s="166" t="n"/>
-      <c r="J102" s="135">
+      <c r="C102" s="165" t="n"/>
+      <c r="D102" s="165" t="n"/>
+      <c r="E102" s="165" t="n"/>
+      <c r="F102" s="165" t="n"/>
+      <c r="G102" s="165" t="n"/>
+      <c r="H102" s="165" t="n"/>
+      <c r="I102" s="165" t="n"/>
+      <c r="J102" s="133">
         <f>SUM(C89:I89)</f>
         <v/>
       </c>
@@ -3531,15 +3531,15 @@
       <c r="A103" s="105" t="n"/>
       <c r="B103" s="58" t="inlineStr">
         <is>
-          <t>약값</t>
-        </is>
-      </c>
-      <c r="C103" s="134" t="n"/>
-      <c r="D103" s="134" t="n"/>
-      <c r="E103" s="134" t="n"/>
-      <c r="F103" s="134" t="n"/>
-      <c r="G103" s="134" t="n"/>
-      <c r="H103" s="134" t="n"/>
+          <t>통원</t>
+        </is>
+      </c>
+      <c r="C103" s="166" t="n"/>
+      <c r="D103" s="166" t="n"/>
+      <c r="E103" s="166" t="n"/>
+      <c r="F103" s="166" t="n"/>
+      <c r="G103" s="166" t="n"/>
+      <c r="H103" s="166" t="n"/>
       <c r="I103" s="166" t="n"/>
       <c r="J103" s="135">
         <f>SUM(C90:I90)</f>
@@ -3550,7 +3550,7 @@
       <c r="A104" s="105" t="n"/>
       <c r="B104" s="58" t="inlineStr">
         <is>
-          <t>MRI/도수치료/비급여주사</t>
+          <t>약값</t>
         </is>
       </c>
       <c r="C104" s="134" t="n"/>
@@ -3560,67 +3560,86 @@
       <c r="G104" s="134" t="n"/>
       <c r="H104" s="134" t="n"/>
       <c r="I104" s="166" t="n"/>
-      <c r="J104" s="129" t="n"/>
+      <c r="J104" s="135">
+        <f>SUM(C91:I91)</f>
+        <v/>
+      </c>
     </row>
     <row r="105" ht="16.5" customHeight="1" s="77">
-      <c r="A105" s="106" t="n"/>
-      <c r="B105" s="22" t="inlineStr">
+      <c r="A105" s="105" t="n"/>
+      <c r="B105" s="58" t="inlineStr">
+        <is>
+          <t>MRI/도수치료/비급여주사</t>
+        </is>
+      </c>
+      <c r="C105" s="134" t="n"/>
+      <c r="D105" s="134" t="n"/>
+      <c r="E105" s="134" t="n"/>
+      <c r="F105" s="134" t="n"/>
+      <c r="G105" s="134" t="n"/>
+      <c r="H105" s="134" t="n"/>
+      <c r="I105" s="166" t="n"/>
+      <c r="J105" s="129" t="n"/>
+    </row>
+    <row r="106" ht="16.5" customHeight="1" s="77">
+      <c r="A106" s="106" t="n"/>
+      <c r="B106" s="22" t="inlineStr">
         <is>
           <t>상해의료비</t>
         </is>
       </c>
-      <c r="C105" s="128" t="n"/>
-      <c r="D105" s="128" t="n"/>
-      <c r="E105" s="128" t="n"/>
-      <c r="F105" s="128" t="n"/>
-      <c r="G105" s="128" t="n"/>
-      <c r="H105" s="128" t="n"/>
-      <c r="I105" s="167" t="n"/>
-      <c r="J105" s="135" t="n"/>
-    </row>
-    <row r="106" ht="16.5" customHeight="1" s="77">
-      <c r="A106" s="104" t="inlineStr">
+      <c r="C106" s="128" t="n"/>
+      <c r="D106" s="128" t="n"/>
+      <c r="E106" s="128" t="n"/>
+      <c r="F106" s="128" t="n"/>
+      <c r="G106" s="128" t="n"/>
+      <c r="H106" s="128" t="n"/>
+      <c r="I106" s="167" t="n"/>
+      <c r="J106" s="135" t="n"/>
+    </row>
+    <row r="107" ht="16.5" customHeight="1" s="77">
+      <c r="A107" s="104" t="inlineStr">
         <is>
           <t>일배책</t>
         </is>
       </c>
-      <c r="B106" s="74" t="inlineStr">
+      <c r="B107" s="74" t="inlineStr">
         <is>
           <t>일상배상책임</t>
         </is>
       </c>
-      <c r="C106" s="168" t="n"/>
-      <c r="D106" s="168" t="n"/>
-      <c r="E106" s="168" t="n"/>
-      <c r="F106" s="168" t="n"/>
-      <c r="G106" s="168" t="n"/>
-      <c r="H106" s="168" t="n"/>
-      <c r="I106" s="168" t="n"/>
-      <c r="J106" s="169">
-        <f>SUM(C91:I91)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="107" ht="16.5" customHeight="1" s="77"/>
+      <c r="C107" s="168" t="n"/>
+      <c r="D107" s="168" t="n"/>
+      <c r="E107" s="168" t="n"/>
+      <c r="F107" s="168" t="n"/>
+      <c r="G107" s="168" t="n"/>
+      <c r="H107" s="168" t="n"/>
+      <c r="I107" s="168" t="n"/>
+      <c r="J107" s="169">
+        <f>SUM(C92:I92)</f>
+        <v/>
+      </c>
+    </row>
     <row r="108" ht="16.5" customHeight="1" s="77"/>
+    <row r="109" ht="16.5" customHeight="1" s="77"/>
   </sheetData>
   <mergeCells count="17">
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A101:A105"/>
-    <mergeCell ref="A32:A40"/>
-    <mergeCell ref="A86:A91"/>
-    <mergeCell ref="A15:A31"/>
-    <mergeCell ref="A92:A94"/>
+    <mergeCell ref="A98:A99"/>
+    <mergeCell ref="A100:A101"/>
+    <mergeCell ref="A87:A92"/>
+    <mergeCell ref="A15:A32"/>
     <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A99:A100"/>
-    <mergeCell ref="A41:A53"/>
-    <mergeCell ref="A54:A66"/>
+    <mergeCell ref="A55:A67"/>
+    <mergeCell ref="A33:A41"/>
+    <mergeCell ref="A11:A14"/>
     <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A11:A14"/>
-    <mergeCell ref="A97:A98"/>
+    <mergeCell ref="A102:A106"/>
+    <mergeCell ref="A42:A54"/>
     <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A67:A85"/>
+    <mergeCell ref="A93:A95"/>
+    <mergeCell ref="A68:A86"/>
     <mergeCell ref="A6:A10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -3634,7 +3653,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.5" defaultRowHeight="16.5"/>
   <cols>
     <col width="5" customWidth="1" style="77" min="1" max="1"/>
@@ -3789,6 +3808,18 @@
       <c r="B14" s="79" t="inlineStr">
         <is>
           <t>엑셀=원천, PPT는 완성 엑셀만 읽음(PDF→엑셀→PPT). 제출 전 렌더검수 통과한 것만.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="0" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B15" s="79" t="inlineStr">
+        <is>
+          <t>소액암(유방·자궁경부·자궁체부·전립선·방광) = 암블록 「소액암」 전용행(유사암 아래). 담보명에 소액암 명시된 진단비만. 유사암 행 합산 금지. PPT 암진단비 「소액암」 칸 1:1. (제228조 2026.10.09)</t>
         </is>
       </c>
     </row>
@@ -4190,7 +4221,7 @@
       </c>
       <c r="D21" s="0" t="inlineStr">
         <is>
-          <t>유사암(갑.기.경.제)</t>
+          <t>소액암</t>
         </is>
       </c>
     </row>
